--- a/data/trans_bre/P1427-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1427-Provincia-trans_bre.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>219,65%</t>
+          <t>147,77%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,47</t>
+          <t>-2,68; 3,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,53</t>
+          <t>-0,09; 5,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,63</t>
+          <t>-0,38; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 158,77</t>
+          <t>-56,94; 224,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 1485,27</t>
+          <t>-31,29; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,55; —</t>
+          <t>-77,65; —</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>84,06%</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,73</t>
+          <t>0,07; 3,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,32</t>
+          <t>0,13; 2,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,5</t>
+          <t>0,01; 3,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 967,93</t>
+          <t>-18,49; 777,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 248,94</t>
+          <t>-2,29; 280,78</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,72%</t>
+          <t>-2,29%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,41</t>
+          <t>-1,57; 2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,97</t>
+          <t>-1,83; 1,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,53</t>
+          <t>-2,93; 2,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-74,45; 471,61</t>
+          <t>-71,81; 342,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 337,11</t>
+          <t>-80,72; 277,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 57,84</t>
+          <t>-38,62; 53,54</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,43%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,48</t>
+          <t>-1,4; 3,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,74</t>
+          <t>-0,53; 2,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,22</t>
+          <t>-1,3; 1,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 288,27</t>
+          <t>-42,77; 331,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 1309,99</t>
+          <t>-62,65; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 110,41</t>
+          <t>-46,66; 172,27</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-19,63%</t>
+          <t>-16,16%</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,22</t>
+          <t>-3,74; 5,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,56</t>
+          <t>1,09; 6,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,75</t>
+          <t>-3,69; 1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 187,17</t>
+          <t>-58,12; 202,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,83; 64,24</t>
+          <t>-59,6; 62,11</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,5</t>
+          <t>-0,87; 2,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,14</t>
+          <t>-0,98; 3,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,86</t>
+          <t>-2,44; 5,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,82; 682,41</t>
+          <t>-50,42; 575,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 53,86</t>
+          <t>-19,74; 59,16</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>103,55%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,7</t>
+          <t>-1,8; 1,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,94</t>
+          <t>-0,51; 2,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,99</t>
+          <t>1,02; 5,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 132,24</t>
+          <t>-55,75; 165,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 241,02</t>
+          <t>-26,52; 287,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 148,29</t>
+          <t>15,84; 233,54</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>213,41%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,09</t>
+          <t>-1,04; 2,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,77</t>
+          <t>0,14; 2,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,83</t>
+          <t>0,08; 2,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 231,92</t>
+          <t>-44,79; 206,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 476,58</t>
+          <t>-2,27; 489,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,59; 883,04</t>
+          <t>-1,51; 238,82</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,51</t>
+          <t>-0,1; 1,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,86</t>
+          <t>0,61; 1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,21</t>
+          <t>0,62; 2,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 89,81</t>
+          <t>-4,5; 87,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48,08; 232,04</t>
+          <t>45,71; 224,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 85,86</t>
+          <t>17,26; 73,34</t>
         </is>
       </c>
     </row>
